--- a/data/Bowil/cost/cost_report.xlsx
+++ b/data/Bowil/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>322.4406629195166</v>
+        <v>288.6132176516143</v>
       </c>
       <c r="C2" t="n">
-        <v>12819.23115361967</v>
+        <v>12968.81077676527</v>
       </c>
       <c r="D2" t="n">
-        <v>-2467.830909830853</v>
+        <v>-2017.048797515547</v>
       </c>
       <c r="E2" t="n">
-        <v>4223.59567513553</v>
+        <v>2990.323941359988</v>
       </c>
       <c r="F2" t="n">
-        <v>32884.24619572364</v>
+        <v>31467.33769270528</v>
       </c>
       <c r="G2" t="n">
-        <v>47781.68277756751</v>
+        <v>45698.03683096661</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1515034627381846</v>
+        <v>0.1448967557810445</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>324.7368279799809</v>
+        <v>289.7121289278468</v>
       </c>
       <c r="C3" t="n">
-        <v>12876.98055916987</v>
+        <v>6383.111577398834</v>
       </c>
       <c r="D3" t="n">
-        <v>-1869.960425879629</v>
+        <v>24347.5195581559</v>
       </c>
       <c r="E3" t="n">
-        <v>4165.570763948341</v>
+        <v>2129.825953411862</v>
       </c>
       <c r="F3" t="n">
-        <v>34296.7371859136</v>
+        <v>20785.70113430059</v>
       </c>
       <c r="G3" t="n">
-        <v>49794.06491113217</v>
+        <v>53935.87035219503</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1578842104193993</v>
+        <v>0.1710168133298074</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>325.8464568998143</v>
+        <v>289.9540330291563</v>
       </c>
       <c r="C4" t="n">
-        <v>6178.173535025588</v>
+        <v>6271.089077798018</v>
       </c>
       <c r="D4" t="n">
-        <v>22482.00156426251</v>
+        <v>23791.53502073832</v>
       </c>
       <c r="E4" t="n">
-        <v>3941.639907740489</v>
+        <v>2118.168248732744</v>
       </c>
       <c r="F4" t="n">
-        <v>23459.19861548888</v>
+        <v>19500.15611377985</v>
       </c>
       <c r="G4" t="n">
-        <v>56386.86007941728</v>
+        <v>51970.90249407808</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1787882732120078</v>
+        <v>0.1647864041569075</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>324.654487965131</v>
+        <v>289.1841297571781</v>
       </c>
       <c r="C5" t="n">
-        <v>6223.851145913668</v>
+        <v>12877.16149093206</v>
       </c>
       <c r="D5" t="n">
-        <v>21981.66471913546</v>
+        <v>-552.9588209097589</v>
       </c>
       <c r="E5" t="n">
-        <v>3898.039246768292</v>
+        <v>2510.762333156526</v>
       </c>
       <c r="F5" t="n">
-        <v>21937.80603277441</v>
+        <v>32635.09248724573</v>
       </c>
       <c r="G5" t="n">
-        <v>54366.01563255696</v>
+        <v>47759.24162018174</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1723806937054461</v>
+        <v>0.1514323075830256</v>
       </c>
     </row>
   </sheetData>
